--- a/src/nodes/HPC/compressor_stage_7_blade_rotor_coordinates_foil.xlsx
+++ b/src/nodes/HPC/compressor_stage_7_blade_rotor_coordinates_foil.xlsx
@@ -357,7 +357,7 @@
         <v>0.00083550508969762287</v>
       </c>
       <c r="B2">
-        <v>0.00085365832124760011</v>
+        <v>0.00080419641993750087</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -365,7 +365,7 @@
         <v>0.0016710101793952457</v>
       </c>
       <c r="B3">
-        <v>0.0012402935076704564</v>
+        <v>0.0011721162923511305</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -373,7 +373,7 @@
         <v>0.002506515269092869</v>
       </c>
       <c r="B4">
-        <v>0.0015569527340490135</v>
+        <v>0.0014743379907797124</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -381,7 +381,7 @@
         <v>0.0033420203587904915</v>
       </c>
       <c r="B5">
-        <v>0.0018257076112529634</v>
+        <v>0.0017314626371350713</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -389,7 +389,7 @@
         <v>0.0041775254484881143</v>
       </c>
       <c r="B6">
-        <v>0.0020555577688724544</v>
+        <v>0.0019518907827666175</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -397,7 +397,7 @@
         <v>0.0050130305381857381</v>
       </c>
       <c r="B7">
-        <v>0.00225164048288409</v>
+        <v>0.0021404180453435426</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -405,7 +405,7 @@
         <v>0.0058485356278833609</v>
       </c>
       <c r="B8">
-        <v>0.0024169766703919363</v>
+        <v>0.0022998647390993633</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -413,7 +413,7 @@
         <v>0.0066840407175809829</v>
       </c>
       <c r="B9">
-        <v>0.0025562881508975205</v>
+        <v>0.0024346386098375466</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -421,7 +421,7 @@
         <v>0.0075195458072786058</v>
       </c>
       <c r="B10">
-        <v>0.0026746727079246212</v>
+        <v>0.0025494982654816248</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -429,7 +429,7 @@
         <v>0.0083550508969762287</v>
       </c>
       <c r="B11">
-        <v>0.0027770310786885571</v>
+        <v>0.0026490183308654465</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -437,7 +437,7 @@
         <v>0.0091905559866738516</v>
       </c>
       <c r="B12">
-        <v>0.0028659796920492251</v>
+        <v>0.0027356413735745854</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -445,7 +445,7 @@
         <v>0.010026061076371476</v>
       </c>
       <c r="B13">
-        <v>0.0029351947897533004</v>
+        <v>0.0028034657152912145</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -453,7 +453,7 @@
         <v>0.010861566166069097</v>
       </c>
       <c r="B14">
-        <v>0.0029808944393703864</v>
+        <v>0.0028489620115185119</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -461,7 +461,7 @@
         <v>0.011697071255766722</v>
       </c>
       <c r="B15">
-        <v>0.0030184041988750095</v>
+        <v>0.0028864344989470905</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -469,7 +469,7 @@
         <v>0.012532576345464343</v>
       </c>
       <c r="B16">
-        <v>0.0030617805908428018</v>
+        <v>0.0029290029490818322</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -477,7 +477,7 @@
         <v>0.013368081435161966</v>
       </c>
       <c r="B17">
-        <v>0.0031008965058488811</v>
+        <v>0.0029672156914972614</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -485,7 +485,7 @@
         <v>0.014203586524859591</v>
       </c>
       <c r="B18">
-        <v>0.0031226741606671031</v>
+        <v>0.0029888670514017935</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -493,7 +493,7 @@
         <v>0.015039091614557212</v>
       </c>
       <c r="B19">
-        <v>0.0031264167088667877</v>
+        <v>0.0029933067784697616</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -501,7 +501,7 @@
         <v>0.015874596704254836</v>
       </c>
       <c r="B20">
-        <v>0.0031145225382161225</v>
+        <v>0.0029827734784919793</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -509,7 +509,7 @@
         <v>0.016710101793952457</v>
       </c>
       <c r="B21">
-        <v>0.0030893900364832925</v>
+        <v>0.0029595057572592591</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -517,7 +517,7 @@
         <v>0.017545606883650082</v>
       </c>
       <c r="B22">
-        <v>0.0030529905656322691</v>
+        <v>0.0029253436269930234</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -525,7 +525,7 @@
         <v>0.018381111973347703</v>
       </c>
       <c r="B23">
-        <v>0.0030055873844101614</v>
+        <v>0.0028805327256371349</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -533,7 +533,7 @@
         <v>0.019216617063045328</v>
       </c>
       <c r="B24">
-        <v>0.0029470167257598639</v>
+        <v>0.0028249200975660666</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -541,7 +541,7 @@
         <v>0.020052122152742952</v>
       </c>
       <c r="B25">
-        <v>0.0028771148226242691</v>
+        <v>0.0027583527871542905</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -549,7 +549,7 @@
         <v>0.020887627242440573</v>
       </c>
       <c r="B26">
-        <v>0.0027956473268652055</v>
+        <v>0.0026806119281695693</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -557,7 +557,7 @@
         <v>0.021723132332138195</v>
       </c>
       <c r="B27">
-        <v>0.0027020975660202334</v>
+        <v>0.0025912150119528242</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -565,7 +565,7 @@
         <v>0.022558637421835819</v>
       </c>
       <c r="B28">
-        <v>0.0025958782865458472</v>
+        <v>0.002489613619238266</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -573,7 +573,7 @@
         <v>0.023394142511533444</v>
       </c>
       <c r="B29">
-        <v>0.0024764022348985411</v>
+        <v>0.0023752593307601062</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -581,7 +581,7 @@
         <v>0.024229647601231065</v>
       </c>
       <c r="B30">
-        <v>0.0023433998256909695</v>
+        <v>0.0022479001819342465</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -589,7 +589,7 @@
         <v>0.025065152690928686</v>
       </c>
       <c r="B31">
-        <v>0.0021978721461604297</v>
+        <v>0.0021084700269033479</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -597,7 +597,7 @@
         <v>0.025900657780626311</v>
       </c>
       <c r="B32">
-        <v>0.0020411379517003745</v>
+        <v>0.0019581991744917608</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -605,7 +605,7 @@
         <v>0.026736162870323932</v>
       </c>
       <c r="B33">
-        <v>0.00187451599770426</v>
+        <v>0.0017983179335238366</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -613,7 +613,7 @@
         <v>0.027571667960021556</v>
       </c>
       <c r="B34">
-        <v>0.001698811014443616</v>
+        <v>0.0016295768183455916</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -621,7 +621,7 @@
         <v>0.028407173049719181</v>
       </c>
       <c r="B35">
-        <v>0.0015127716317022675</v>
+        <v>0.0014508071653897021</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -629,7 +629,7 @@
         <v>0.0292426781394168</v>
       </c>
       <c r="B36">
-        <v>0.0013146324541421142</v>
+        <v>0.00126036051661051</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -637,7 +637,7 @@
         <v>0.030078183229114423</v>
       </c>
       <c r="B37">
-        <v>0.0011026280864250529</v>
+        <v>0.0010565884139623549</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -645,7 +645,7 @@
         <v>0.030913688318812048</v>
       </c>
       <c r="B38">
-        <v>0.00087373296435008178</v>
+        <v>0.00083666620715322027</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -653,7 +653,7 @@
         <v>0.031749193408509672</v>
       </c>
       <c r="B39">
-        <v>0.00061988084826458884</v>
+        <v>0.00059306447690565388</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -661,7 +661,7 @@
         <v>0.0325846984982073</v>
       </c>
       <c r="B40">
-        <v>0.00033174532965306059</v>
+        <v>0.00031707761169584526</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -677,7 +677,7 @@
         <v>0.033420203587904915</v>
       </c>
       <c r="B42">
-        <v>-1.4870539210248853E-17</v>
+        <v>-1.4841551804380921E-17</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -685,7 +685,7 @@
         <v>0.0325846984982073</v>
       </c>
       <c r="B43">
-        <v>-0.00010828620906340062</v>
+        <v>-9.3618491106185162E-05</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -693,7 +693,7 @@
         <v>0.031749193408509672</v>
       </c>
       <c r="B44">
-        <v>-0.0001846102925034568</v>
+        <v>-0.00015779392114452189</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -701,7 +701,7 @@
         <v>0.030913688318812048</v>
       </c>
       <c r="B45">
-        <v>-0.00023826975155575851</v>
+        <v>-0.00020120299435889716</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -709,7 +709,7 @@
         <v>0.030078183229114423</v>
       </c>
       <c r="B46">
-        <v>-0.00027856208745588134</v>
+        <v>-0.00023252241499318357</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -717,7 +717,7 @@
         <v>0.0292426781394168</v>
       </c>
       <c r="B47">
-        <v>-0.00031352567180600009</v>
+        <v>-0.00025925373427439626</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -725,7 +725,7 @@
         <v>0.028407173049719181</v>
       </c>
       <c r="B48">
-        <v>-0.00034616235767468534</v>
+        <v>-0.00028419789136212021</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -733,7 +733,7 @@
         <v>0.027571667960021556</v>
       </c>
       <c r="B49">
-        <v>-0.00037821486849710755</v>
+        <v>-0.00030898067239908334</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -741,7 +741,7 @@
         <v>0.026736162870323932</v>
       </c>
       <c r="B50">
-        <v>-0.00041142592770843637</v>
+        <v>-0.000335227863528013</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -749,7 +749,7 @@
         <v>0.025900657780626311</v>
       </c>
       <c r="B51">
-        <v>-0.000447025364558034</v>
+        <v>-0.0003640865873494203</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -757,7 +757,7 @@
         <v>0.025065152690928686</v>
       </c>
       <c r="B52">
-        <v>-0.00048419143155203177</v>
+        <v>-0.00039478931229494966</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -765,7 +765,7 @@
         <v>0.024229647601231065</v>
       </c>
       <c r="B53">
-        <v>-0.00052158948701075273</v>
+        <v>-0.00042608984325402866</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -773,7 +773,7 @@
         <v>0.023394142511533444</v>
       </c>
       <c r="B54">
-        <v>-0.000557884889254521</v>
+        <v>-0.00045674198511608559</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -781,7 +781,7 @@
         <v>0.022558637421835819</v>
       </c>
       <c r="B55">
-        <v>-0.00059206173268160588</v>
+        <v>-0.00048579706537402406</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -789,7 +789,7 @@
         <v>0.021723132332138195</v>
       </c>
       <c r="B56">
-        <v>-0.00062437905600206257</v>
+        <v>-0.0005134965019346527</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -797,7 +797,7 @@
         <v>0.020887627242440573</v>
       </c>
       <c r="B57">
-        <v>-0.00065541463400389257</v>
+        <v>-0.00054037923530825586</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -805,7 +805,7 @@
         <v>0.020052122152742952</v>
       </c>
       <c r="B58">
-        <v>-0.00068574624147509718</v>
+        <v>-0.00056698420600511811</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -813,7 +813,7 @@
         <v>0.019216617063045328</v>
       </c>
       <c r="B59">
-        <v>-0.00071588212005405344</v>
+        <v>-0.00059378549186025608</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -821,7 +821,7 @@
         <v>0.018381111973347703</v>
       </c>
       <c r="B60">
-        <v>-0.00074605237878063964</v>
+        <v>-0.00062099772000761275</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -829,7 +829,7 @@
         <v>0.017545606883650082</v>
       </c>
       <c r="B61">
-        <v>-0.0007764175935451096</v>
+        <v>-0.00064877065490586338</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -837,7 +837,7 @@
         <v>0.016710101793952457</v>
       </c>
       <c r="B62">
-        <v>-0.00080713834023771669</v>
+        <v>-0.00067725406101368289</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -845,7 +845,7 @@
         <v>0.015874596704254836</v>
       </c>
       <c r="B63">
-        <v>-0.0008379492535081698</v>
+        <v>-0.00070620019378402651</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -853,7 +853,7 @@
         <v>0.015039091614557212</v>
       </c>
       <c r="B64">
-        <v>-0.00086688120304399721</v>
+        <v>-0.0007337712726469709</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -861,7 +861,7 @@
         <v>0.014203586524859591</v>
       </c>
       <c r="B65">
-        <v>-0.00089153911729218248</v>
+        <v>-0.00075773200802687279</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -869,7 +869,7 @@
         <v>0.013368081435161966</v>
       </c>
       <c r="B66">
-        <v>-0.00090952792469970866</v>
+        <v>-0.00077584711034808882</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -877,7 +877,7 @@
         <v>0.012532576345464343</v>
       </c>
       <c r="B67">
-        <v>-0.00092154866198628925</v>
+        <v>-0.00078877102022531943</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -885,7 +885,7 @@
         <v>0.011697071255766722</v>
       </c>
       <c r="B68">
-        <v>-0.00094068679896255826</v>
+        <v>-0.00080871709903463935</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -893,7 +893,7 @@
         <v>0.010861566166069097</v>
       </c>
       <c r="B69">
-        <v>-0.00097707839618583776</v>
+        <v>-0.00084514596833396342</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -901,7 +901,7 @@
         <v>0.010026061076371476</v>
       </c>
       <c r="B70">
-        <v>-0.0010166774441092796</v>
+        <v>-0.00088494836964719337</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -909,7 +909,7 @@
         <v>0.0091905559866738516</v>
       </c>
       <c r="B71">
-        <v>-0.0010441698621899544</v>
+        <v>-0.000913831543715315</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -917,7 +917,7 @@
         <v>0.0083550508969762287</v>
       </c>
       <c r="B72">
-        <v>-0.0010633513560047718</v>
+        <v>-0.00093533860818166071</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -925,7 +925,7 @@
         <v>0.0075195458072786058</v>
       </c>
       <c r="B73">
-        <v>-0.0010805605653652743</v>
+        <v>-0.00095538612292227763</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -933,7 +933,7 @@
         <v>0.0066840407175809829</v>
       </c>
       <c r="B74">
-        <v>-0.0010931980809016967</v>
+        <v>-0.00097154853984172268</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -941,7 +941,7 @@
         <v>0.0058485356278833609</v>
       </c>
       <c r="B75">
-        <v>-0.0010963812683852474</v>
+        <v>-0.00097926933709267458</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -949,7 +949,7 @@
         <v>0.0050130305381857381</v>
       </c>
       <c r="B76">
-        <v>-0.0010850326433323363</v>
+        <v>-0.00097381020579178864</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -957,7 +957,7 @@
         <v>0.0041775254484881143</v>
       </c>
       <c r="B77">
-        <v>-0.0010544518143026514</v>
+        <v>-0.0009507848281968146</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -965,7 +965,7 @@
         <v>0.0033420203587904915</v>
       </c>
       <c r="B78">
-        <v>-0.0010016416122837918</v>
+        <v>-0.00090739663816589988</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -973,7 +973,7 @@
         <v>0.002506515269092869</v>
       </c>
       <c r="B79">
-        <v>-0.00092148956403001491</v>
+        <v>-0.00083887482076071382</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -981,7 +981,7 @@
         <v>0.0016710101793952457</v>
       </c>
       <c r="B80">
-        <v>-0.00080502295190932368</v>
+        <v>-0.00073684573658999762</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -989,7 +989,7 @@
         <v>0.00083550508969762287</v>
       </c>
       <c r="B81">
-        <v>-0.000630198718055378</v>
+        <v>-0.00058073681674527871</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1023,7 +1023,7 @@
         <v>0.00096711311085415606</v>
       </c>
       <c r="B2">
-        <v>0.00042918069188039595</v>
+        <v>0.0003304191009999696</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1031,7 +1031,7 @@
         <v>0.0019342262217083121</v>
       </c>
       <c r="B3">
-        <v>0.000632248051893432</v>
+        <v>0.000496117210409601</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1039,7 +1039,7 @@
         <v>0.0029013393325624686</v>
       </c>
       <c r="B4">
-        <v>0.00080069339456933879</v>
+        <v>0.00063573484547716733</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1047,7 +1047,7 @@
         <v>0.0038684524434166243</v>
       </c>
       <c r="B5">
-        <v>0.0009451577213959256</v>
+        <v>0.00075697685228592383</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1055,7 +1055,7 @@
         <v>0.00483556555427078</v>
       </c>
       <c r="B6">
-        <v>0.0010699776662575259</v>
+        <v>0.00086298367293319268</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1063,7 +1063,7 @@
         <v>0.0058026786651249372</v>
       </c>
       <c r="B7">
-        <v>0.0011776273633339793</v>
+        <v>0.000955547245462318</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1071,7 +1071,7 @@
         <v>0.0067697917759790933</v>
       </c>
       <c r="B8">
-        <v>0.0012695603829631509</v>
+        <v>0.0010357205923529976</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1079,7 +1079,7 @@
         <v>0.0077369048868332485</v>
       </c>
       <c r="B9">
-        <v>0.0013480509805199206</v>
+        <v>0.0011051508515977906</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1087,7 +1087,7 @@
         <v>0.0087040179976874046</v>
       </c>
       <c r="B10">
-        <v>0.0014155549036523585</v>
+        <v>0.001165616531980493</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1095,7 +1095,7 @@
         <v>0.00967113110854156</v>
       </c>
       <c r="B11">
-        <v>0.0014744331840642745</v>
+        <v>0.001218827509936987</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1103,7 +1103,7 @@
         <v>0.010638244219395717</v>
       </c>
       <c r="B12">
-        <v>0.0015259452894960984</v>
+        <v>0.0012656961008421488</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1111,7 +1111,7 @@
         <v>0.011605357330249875</v>
       </c>
       <c r="B13">
-        <v>0.001567039147778997</v>
+        <v>0.0013040130081747479</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1119,7 +1119,7 @@
         <v>0.012572470441104029</v>
       </c>
       <c r="B14">
-        <v>0.0015958887680575617</v>
+        <v>0.0013324565885770754</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1127,7 +1127,7 @@
         <v>0.013539583551958187</v>
       </c>
       <c r="B15">
-        <v>0.0016198840246393403</v>
+        <v>0.0013563774232416188</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1135,7 +1135,7 @@
         <v>0.014506696662812341</v>
       </c>
       <c r="B16">
-        <v>0.0016458028748704504</v>
+        <v>0.0013806830394753</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1143,7 +1143,7 @@
         <v>0.015473809773666497</v>
       </c>
       <c r="B17">
-        <v>0.0016687597430883323</v>
+        <v>0.0014018365244925855</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1151,7 +1151,7 @@
         <v>0.016440922884520655</v>
       </c>
       <c r="B18">
-        <v>0.0016824461251924985</v>
+        <v>0.0014152707309572038</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1159,7 +1159,7 @@
         <v>0.017408035995374809</v>
       </c>
       <c r="B19">
-        <v>0.0016865253363394341</v>
+        <v>0.0014207420134223891</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1167,7 +1167,7 @@
         <v>0.018375149106228967</v>
       </c>
       <c r="B20">
-        <v>0.0016821536464998667</v>
+        <v>0.00141908760191375</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1175,7 +1175,7 @@
         <v>0.019342262217083121</v>
       </c>
       <c r="B21">
-        <v>0.0016704873256445244</v>
+        <v>0.0014111447264568966</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1183,7 +1183,7 @@
         <v>0.020309375327937279</v>
       </c>
       <c r="B22">
-        <v>0.0016524768435634636</v>
+        <v>0.0013976015881220793</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1191,7 +1191,7 @@
         <v>0.021276488438791433</v>
       </c>
       <c r="B23">
-        <v>0.0016282494693240569</v>
+        <v>0.0013785502721581117</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1199,7 +1199,7 @@
         <v>0.022243601549645591</v>
       </c>
       <c r="B24">
-        <v>0.0015977266718130044</v>
+        <v>0.0013539338348584492</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1207,7 +1207,7 @@
         <v>0.023210714660499749</v>
       </c>
       <c r="B25">
-        <v>0.0015608299199170081</v>
+        <v>0.0013236953325165466</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1215,7 +1215,7 @@
         <v>0.024177827771353903</v>
       </c>
       <c r="B26">
-        <v>0.0015174467906758622</v>
+        <v>0.0012877532552107091</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1223,7 +1223,7 @@
         <v>0.025144940882208058</v>
       </c>
       <c r="B27">
-        <v>0.0014673292937417333</v>
+        <v>0.0012459278281586402</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1231,7 +1231,7 @@
         <v>0.026112053993062215</v>
       </c>
       <c r="B28">
-        <v>0.0014101955469198811</v>
+        <v>0.0011980147103628938</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1239,7 +1239,7 @@
         <v>0.027079167103916373</v>
       </c>
       <c r="B29">
-        <v>0.0013457636680155659</v>
+        <v>0.0011438095608260236</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1247,7 +1247,7 @@
         <v>0.028046280214770528</v>
       </c>
       <c r="B30">
-        <v>0.0012739051394457764</v>
+        <v>0.0010832190457835769</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1255,7 +1255,7 @@
         <v>0.029013393325624682</v>
       </c>
       <c r="B31">
-        <v>0.001195104902074416</v>
+        <v>0.001016593860403072</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1263,7 +1263,7 @@
         <v>0.02998050643647884</v>
       </c>
       <c r="B32">
-        <v>0.0011100012613771157</v>
+        <v>0.00094439570708501988</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1271,7 +1271,7 @@
         <v>0.030947619547332994</v>
       </c>
       <c r="B33">
-        <v>0.0010192325228295075</v>
+        <v>0.00086708628822993155</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1279,7 +1279,7 @@
         <v>0.031914732658187152</v>
       </c>
       <c r="B34">
-        <v>0.00092318924243805546</v>
+        <v>0.000784947905795945</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1287,7 +1287,7 @@
         <v>0.03288184576904131</v>
       </c>
       <c r="B35">
-        <v>0.00082127097833255454</v>
+        <v>0.00069754525997170415</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1295,7 +1295,7 @@
         <v>0.03384895887989546</v>
       </c>
       <c r="B36">
-        <v>0.00071262953917363282</v>
+        <v>0.00060426365050347982</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1303,7 +1303,7 @@
         <v>0.034816071990749618</v>
       </c>
       <c r="B37">
-        <v>0.00059641673362191691</v>
+        <v>0.00050448837713754167</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1311,7 +1311,7 @@
         <v>0.035783185101603776</v>
       </c>
       <c r="B38">
-        <v>0.00047117674501460249</v>
+        <v>0.00039716479212606578</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1319,7 +1319,7 @@
         <v>0.036750298212457934</v>
       </c>
       <c r="B39">
-        <v>0.00033302325539515554</v>
+        <v>0.0002794784577448488</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1327,7 +1327,7 @@
         <v>0.037717411323312092</v>
       </c>
       <c r="B40">
-        <v>0.00017746232148360986</v>
+        <v>0.00014817498877559268</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -1343,7 +1343,7 @@
         <v>0.038684524434166243</v>
       </c>
       <c r="B42">
-        <v>-8.3883690866183239E-21</v>
+        <v>1.3106826697841132E-21</v>
       </c>
     </row>
     <row r="43" spans="1:2">
@@ -1351,7 +1351,7 @@
         <v>0.037717411323312092</v>
       </c>
       <c r="B43">
-        <v>-3.4764727125210406E-05</v>
+        <v>-5.4773944171932089E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -1359,7 +1359,7 @@
         <v>0.036750298212457934</v>
       </c>
       <c r="B44">
-        <v>-5.4982524679531175E-05</v>
+        <v>-1.4377270292244207E-06</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -1367,7 +1367,7 @@
         <v>0.035783185101603776</v>
       </c>
       <c r="B45">
-        <v>-6.5141754177692741E-05</v>
+        <v>8.8701987108439743E-06</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -1375,7 +1375,7 @@
         <v>0.034816071990749618</v>
       </c>
       <c r="B46">
-        <v>-6.9730777134425738E-05</v>
+        <v>2.2197579349949526E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -1383,7 +1383,7 @@
         <v>0.03384895887989546</v>
       </c>
       <c r="B47">
-        <v>-7.2630523653563058E-05</v>
+        <v>3.5735365016589961E-05</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -1391,7 +1391,7 @@
         <v>0.03288184576904131</v>
       </c>
       <c r="B48">
-        <v>-7.5292198195346741E-05</v>
+        <v>4.8433520165503629E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -1399,7 +1399,7 @@
         <v>0.031914732658187152</v>
       </c>
       <c r="B49">
-        <v>-7.8559573809121154E-05</v>
+        <v>5.96817628329892E-05</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -1407,7 +1407,7 @@
         <v>0.030947619547332994</v>
       </c>
       <c r="B50">
-        <v>-8.3276423544230646E-05</v>
+        <v>6.886981105534522E-05</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -1415,7 +1415,7 @@
         <v>0.02998050643647884</v>
       </c>
       <c r="B51">
-        <v>-9.003898711633261E-05</v>
+        <v>7.5566567175763266E-05</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -1423,7 +1423,7 @@
         <v>0.029013393325624682</v>
       </c>
       <c r="B52">
-        <v>-9.8453370906336773E-05</v>
+        <v>8.00576707650071E-05</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -1431,7 +1431,7 @@
         <v>0.028046280214770528</v>
       </c>
       <c r="B53">
-        <v>-0.0001078781479614659</v>
+        <v>8.28079457007335E-05</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -1439,7 +1439,7 @@
         <v>0.027079167103916373</v>
       </c>
       <c r="B54">
-        <v>-0.00011767189132894288</v>
+        <v>8.4282215860599283E-05</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -1447,7 +1447,7 @@
         <v>0.026112053993062215</v>
       </c>
       <c r="B55">
-        <v>-0.00012734674697133222</v>
+        <v>8.4834089585655159E-05</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -1455,7 +1455,7 @@
         <v>0.025144940882208058</v>
       </c>
       <c r="B56">
-        <v>-0.00013702915251256539</v>
+        <v>8.4372313070527793E-05</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -1463,7 +1463,7 @@
         <v>0.024177827771353903</v>
       </c>
       <c r="B57">
-        <v>-0.00014699911849191559</v>
+        <v>8.2694416973237762E-05</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -1471,7 +1471,7 @@
         <v>0.023210714660499749</v>
       </c>
       <c r="B58">
-        <v>-0.000157536655448656</v>
+        <v>7.9597931951805689E-05</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -1479,7 +1479,7 @@
         <v>0.022243601549645591</v>
       </c>
       <c r="B59">
-        <v>-0.00016888808872725185</v>
+        <v>7.490474822730352E-05</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -1487,7 +1487,7 @@
         <v>0.021276488438791433</v>
       </c>
       <c r="B60">
-        <v>-0.0001811650028929363</v>
+        <v>6.8534194273008709E-05</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -1495,7 +1495,7 @@
         <v>0.020309375327937279</v>
       </c>
       <c r="B61">
-        <v>-0.00019444529731613448</v>
+        <v>6.0429958125250011E-05</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -1503,7 +1503,7 @@
         <v>0.019342262217083121</v>
       </c>
       <c r="B62">
-        <v>-0.00020880687136727152</v>
+        <v>5.053572782035626E-05</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -1511,7 +1511,7 @@
         <v>0.018375149106228967</v>
       </c>
       <c r="B63">
-        <v>-0.00022412203890677675</v>
+        <v>3.8944005679340026E-05</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -1519,7 +1519,7 @@
         <v>0.017408035995374809</v>
       </c>
       <c r="B64">
-        <v>-0.00023944077175509632</v>
+        <v>2.6342551161948847E-05</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -1527,7 +1527,7 @@
         <v>0.016440922884520655</v>
       </c>
       <c r="B65">
-        <v>-0.00025360745622268061</v>
+        <v>1.3567938012614137E-05</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -1535,7 +1535,7 @@
         <v>0.015473809773666497</v>
       </c>
       <c r="B66">
-        <v>-0.00026546647861997987</v>
+        <v>1.4567399757671855E-06</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -1543,7 +1543,7 @@
         <v>0.014506696662812341</v>
       </c>
       <c r="B67">
-        <v>-0.00027535535263064221</v>
+        <v>-1.023551723549143E-05</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -1551,7 +1551,7 @@
         <v>0.013539583551958187</v>
       </c>
       <c r="B68">
-        <v>-0.00028958410143110588</v>
+        <v>-2.6077500033384349E-05</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -1559,7 +1559,7 @@
         <v>0.012572470441104029</v>
       </c>
       <c r="B69">
-        <v>-0.000313040068757556</v>
+        <v>-4.9607889277069789E-05</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -1567,7 +1567,7 @@
         <v>0.011605357330249875</v>
       </c>
       <c r="B70">
-        <v>-0.00033894737109237377</v>
+        <v>-7.5921231488124534E-05</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -1575,7 +1575,7 @@
         <v>0.010638244219395717</v>
       </c>
       <c r="B71">
-        <v>-0.00035991839640208583</v>
+        <v>-9.96692077481364E-05</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -1583,7 +1583,7 @@
         <v>0.00967113110854156</v>
       </c>
       <c r="B72">
-        <v>-0.00037778184584360522</v>
+        <v>-0.00012217617171631783</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -1591,7 +1591,7 @@
         <v>0.0087040179976874046</v>
       </c>
       <c r="B73">
-        <v>-0.00039559271715825889</v>
+        <v>-0.00014565434548639372</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>0.0077369048868332485</v>
       </c>
       <c r="B74">
-        <v>-0.00041209488123464374</v>
+        <v>-0.00016919475231251389</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>0.0067697917759790933</v>
       </c>
       <c r="B75">
-        <v>-0.000424930853342308</v>
+        <v>-0.00019109106273215479</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>0.0058026786651249372</v>
       </c>
       <c r="B76">
-        <v>-0.00043164885312733638</v>
+        <v>-0.0002095687352556748</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>0.00483556555427078</v>
       </c>
       <c r="B77">
-        <v>-0.00042997880710720661</v>
+        <v>-0.00022298481378287349</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -1631,7 +1631,7 @@
         <v>0.0038684524434166243</v>
       </c>
       <c r="B78">
-        <v>-0.00041847176490843435</v>
+        <v>-0.00023029089579843266</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -1639,7 +1639,7 @@
         <v>0.0029013393325624686</v>
       </c>
       <c r="B79">
-        <v>-0.00039465841044639816</v>
+        <v>-0.00022969986135422651</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -1647,7 +1647,7 @@
         <v>0.0019342262217083121</v>
       </c>
       <c r="B80">
-        <v>-0.000354207321177807</v>
+        <v>-0.0002180764796939761</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -1655,7 +1655,7 @@
         <v>0.00096711311085415606</v>
       </c>
       <c r="B81">
-        <v>-0.00028648301015167949</v>
+        <v>-0.00018772141927125315</v>
       </c>
     </row>
     <row r="82" spans="1:2">
@@ -1689,7 +1689,7 @@
         <v>0.0010861566166069099</v>
       </c>
       <c r="B2">
-        <v>0.00029329894012240592</v>
+        <v>0.00021292335049349461</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1697,7 +1697,7 @@
         <v>0.0021723132332138197</v>
       </c>
       <c r="B3">
-        <v>0.00043402706588683394</v>
+        <v>0.00032323909099292924</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1705,7 +1705,7 @@
         <v>0.00325846984982073</v>
       </c>
       <c r="B4">
-        <v>0.00055122068590519012</v>
+        <v>0.00041697172809257611</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1713,7 +1713,7 @@
         <v>0.0043446264664276394</v>
       </c>
       <c r="B5">
-        <v>0.0006520492871528573</v>
+        <v>0.000498901204211283</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1721,7 +1721,7 @@
         <v>0.0054307830830345486</v>
       </c>
       <c r="B6">
-        <v>0.00073943418298229649</v>
+        <v>0.00057097533056031148</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1729,7 +1729,7 @@
         <v>0.00651693969964146</v>
       </c>
       <c r="B7">
-        <v>0.00081504170427774394</v>
+        <v>0.000634305243274354</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1737,7 +1737,7 @@
         <v>0.0076030963162483688</v>
       </c>
       <c r="B8">
-        <v>0.00087985050623062269</v>
+        <v>0.00068954361788019182</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -1745,7 +1745,7 @@
         <v>0.0086892529328552789</v>
       </c>
       <c r="B9">
-        <v>0.000935392346928775</v>
+        <v>0.00073771184270631722</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -1753,7 +1753,7 @@
         <v>0.0097754095494621881</v>
       </c>
       <c r="B10">
-        <v>0.00098332132316522212</v>
+        <v>0.00077991285419535259</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -1761,7 +1761,7 @@
         <v>0.010861566166069097</v>
       </c>
       <c r="B11">
-        <v>0.0010252277836572856</v>
+        <v>0.00081720706844473027</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1769,7 +1769,7 @@
         <v>0.011947722782676008</v>
       </c>
       <c r="B12">
-        <v>0.0010619598207745617</v>
+        <v>0.00085016005325327286</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1777,7 +1777,7 @@
         <v>0.013033879399282919</v>
       </c>
       <c r="B13">
-        <v>0.0010914602495714458</v>
+        <v>0.000877400503570556</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -1785,7 +1785,7 @@
         <v>0.014120036015889827</v>
       </c>
       <c r="B14">
-        <v>0.0011124981252551337</v>
+        <v>0.00089810792999583835</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -1793,7 +1793,7 @@
         <v>0.015206192632496738</v>
       </c>
       <c r="B15">
-        <v>0.0011300527409592225</v>
+        <v>0.00091560197857635411</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -1801,7 +1801,7 @@
         <v>0.016292349249103645</v>
       </c>
       <c r="B16">
-        <v>0.0011486910807825932</v>
+        <v>0.00093292741292101721</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -1809,7 +1809,7 @@
         <v>0.017378505865710558</v>
       </c>
       <c r="B17">
-        <v>0.0011651206547588623</v>
+        <v>0.00094788933143748026</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -1817,7 +1817,7 @@
         <v>0.018464662482317467</v>
       </c>
       <c r="B18">
-        <v>0.0011750901707062444</v>
+        <v>0.00095765361815011653</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -1825,7 +1825,7 @@
         <v>0.019550819098924376</v>
       </c>
       <c r="B19">
-        <v>0.0011783726016466106</v>
+        <v>0.00096206896475144318</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -1833,7 +1833,7 @@
         <v>0.020636975715531285</v>
       </c>
       <c r="B20">
-        <v>0.001175746986902746</v>
+        <v>0.00096165476485101352</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -1841,7 +1841,7 @@
         <v>0.021723132332138195</v>
       </c>
       <c r="B21">
-        <v>0.0011679923657974356</v>
+        <v>0.000956930412058381</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -1849,7 +1849,7 @@
         <v>0.022809288948745104</v>
       </c>
       <c r="B22">
-        <v>0.0011557491370830493</v>
+        <v>0.00094832286179427465</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -1857,7 +1857,7 @@
         <v>0.023895445565352016</v>
       </c>
       <c r="B23">
-        <v>0.001139103137230296</v>
+        <v>0.00093588931672412758</v>
       </c>
     </row>
     <row r="24" spans="1:2">
@@ -1865,7 +1865,7 @@
         <v>0.024981602181958926</v>
       </c>
       <c r="B24">
-        <v>0.0011180015621394695</v>
+        <v>0.00091959454132454891</v>
       </c>
     </row>
     <row r="25" spans="1:2">
@@ -1873,7 +1873,7 @@
         <v>0.026067758798565838</v>
       </c>
       <c r="B25">
-        <v>0.0010923916077108635</v>
+        <v>0.00089940330007214758</v>
       </c>
     </row>
     <row r="26" spans="1:2">
@@ -1881,7 +1881,7 @@
         <v>0.027153915415172744</v>
       </c>
       <c r="B26">
-        <v>0.0010621976691356954</v>
+        <v>0.00087526514625528584</v>
       </c>
     </row>
     <row r="27" spans="1:2">
@@ -1889,7 +1889,7 @@
         <v>0.028240072031779653</v>
       </c>
       <c r="B27">
-        <v>0.0010272529387688788</v>
+        <v>0.00084706878840933779</v>
       </c>
     </row>
     <row r="28" spans="1:2">
@@ -1897,7 +1897,7 @@
         <v>0.029326228648386566</v>
       </c>
       <c r="B28">
-        <v>0.00098736780825625084</v>
+        <v>0.00081468772388143052</v>
       </c>
     </row>
     <row r="29" spans="1:2">
@@ -1905,7 +1905,7 @@
         <v>0.030412385264993475</v>
       </c>
       <c r="B29">
-        <v>0.000942352669243649</v>
+        <v>0.00077799545001869155</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -1913,7 +1913,7 @@
         <v>0.031498541881600388</v>
       </c>
       <c r="B30">
-        <v>0.00089212129675239041</v>
+        <v>0.00073693437564771385</v>
       </c>
     </row>
     <row r="31" spans="1:2">
@@ -1921,7 +1921,7 @@
         <v>0.03258469849820729</v>
       </c>
       <c r="B31">
-        <v>0.00083700099930571258</v>
+        <v>0.00069172255551295419</v>
       </c>
     </row>
     <row r="32" spans="1:2">
@@ -1929,7 +1929,7 @@
         <v>0.0336708551148142</v>
       </c>
       <c r="B32">
-        <v>0.00077742246880233175</v>
+        <v>0.00064264695583833456</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -1937,7 +1937,7 @@
         <v>0.034757011731421115</v>
       </c>
       <c r="B33">
-        <v>0.00071381639714096544</v>
+        <v>0.00058999454284777762</v>
       </c>
     </row>
     <row r="34" spans="1:2">
@@ -1945,7 +1945,7 @@
         <v>0.035843168348028025</v>
       </c>
       <c r="B34">
-        <v>0.00064644656848117127</v>
+        <v>0.000533940999821882</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -1953,7 +1953,7 @@
         <v>0.036929324964634934</v>
       </c>
       <c r="B35">
-        <v>0.00057490913602586935</v>
+        <v>0.00047421687826795106</v>
       </c>
     </row>
     <row r="36" spans="1:2">
@@ -1961,7 +1961,7 @@
         <v>0.038015481581241843</v>
       </c>
       <c r="B36">
-        <v>0.000498633345238821</v>
+        <v>0.00041044144674996487</v>
       </c>
     </row>
     <row r="37" spans="1:2">
@@ -1969,7 +1969,7 @@
         <v>0.039101638197848752</v>
       </c>
       <c r="B37">
-        <v>0.00041704844158378646</v>
+        <v>0.00034223397383190249</v>
       </c>
     </row>
     <row r="38" spans="1:2">
@@ -1977,7 +1977,7 @@
         <v>0.040187794814455662</v>
       </c>
       <c r="B38">
-        <v>0.00032917425478141721</v>
+        <v>0.0002689407743365175</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -1985,7 +1985,7 @@
         <v>0.041273951431062571</v>
       </c>
       <c r="B39">
-        <v>0.00023239295157992688</v>
+        <v>0.00018881634812165774</v>
       </c>
     </row>
     <row r="40" spans="1:2">
@@ -1993,7 +1993,7 @@
         <v>0.04236010804766948</v>
       </c>
       <c r="B40">
-        <v>0.00012367728298441955</v>
+        <v>9.98422413039446E-05</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -2017,7 +2017,7 @@
         <v>0.04236010804766948</v>
       </c>
       <c r="B43">
-        <v>-1.933296709843031E-05</v>
+        <v>4.50207458204469E-06</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -2025,7 +2025,7 @@
         <v>0.041273951431062571</v>
       </c>
       <c r="B44">
-        <v>-2.9066669169687922E-05</v>
+        <v>1.4509934288581233E-05</v>
       </c>
     </row>
     <row r="45" spans="1:2">
@@ -2033,7 +2033,7 @@
         <v>0.040187794814455662</v>
       </c>
       <c r="B45">
-        <v>-3.2226627887980839E-05</v>
+        <v>2.8006852556918853E-05</v>
       </c>
     </row>
     <row r="46" spans="1:2">
@@ -2041,7 +2041,7 @@
         <v>0.039101638197848752</v>
       </c>
       <c r="B46">
-        <v>-3.1838364927517176E-05</v>
+        <v>4.2976102824366782E-05</v>
       </c>
     </row>
     <row r="47" spans="1:2">
@@ -2049,7 +2049,7 @@
         <v>0.038015481581241843</v>
       </c>
       <c r="B47">
-        <v>-3.0518045694316015E-05</v>
+        <v>5.7673852794540193E-05</v>
       </c>
     </row>
     <row r="48" spans="1:2">
@@ -2057,7 +2057,7 @@
         <v>0.036929324964634934</v>
       </c>
       <c r="B48">
-        <v>-2.9244410521640316E-05</v>
+        <v>7.1447847236278E-05</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -2065,7 +2065,7 @@
         <v>0.035843168348028025</v>
       </c>
       <c r="B49">
-        <v>-2.8586843474563988E-05</v>
+        <v>8.3918725184725236E-05</v>
       </c>
     </row>
     <row r="50" spans="1:2">
@@ -2073,7 +2073,7 @@
         <v>0.034757011731421115</v>
       </c>
       <c r="B50">
-        <v>-2.9114728618160963E-05</v>
+        <v>9.4707125675026782E-05</v>
       </c>
     </row>
     <row r="51" spans="1:2">
@@ -2081,7 +2081,7 @@
         <v>0.0336708551148142</v>
       </c>
       <c r="B51">
-        <v>-3.1230608981651047E-05</v>
+        <v>0.00010354490398234612</v>
       </c>
     </row>
     <row r="52" spans="1:2">
@@ -2089,7 +2089,7 @@
         <v>0.03258469849820729</v>
       </c>
       <c r="B52">
-        <v>-3.4669663450837504E-05</v>
+        <v>0.00011060878034192086</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -2097,7 +2097,7 @@
         <v>0.031498541881600388</v>
       </c>
       <c r="B53">
-        <v>-3.900022987566947E-05</v>
+        <v>0.00011618669122900721</v>
       </c>
     </row>
     <row r="54" spans="1:2">
@@ -2105,7 +2105,7 @@
         <v>0.030412385264993475</v>
       </c>
       <c r="B54">
-        <v>-4.3790646106096135E-05</v>
+        <v>0.00012056657311886144</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -2113,7 +2113,7 @@
         <v>0.029326228648386566</v>
       </c>
       <c r="B55">
-        <v>-4.8712697992671274E-05</v>
+        <v>0.00012396738638214915</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -2121,7 +2121,7 @@
         <v>0.028240072031779653</v>
       </c>
       <c r="B56">
-        <v>-5.3851963388367341E-05</v>
+        <v>0.00012633218697117376</v>
       </c>
     </row>
     <row r="57" spans="1:2">
@@ -2129,7 +2129,7 @@
         <v>0.027153915415172744</v>
       </c>
       <c r="B57">
-        <v>-5.9397468146761442E-05</v>
+        <v>0.00012753505473364813</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -2137,7 +2137,7 @@
         <v>0.026067758798565838</v>
       </c>
       <c r="B58">
-        <v>-6.5538238121430636E-05</v>
+        <v>0.00012745006951728511</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -2145,7 +2145,7 @@
         <v>0.024981602181958926</v>
       </c>
       <c r="B59">
-        <v>-7.2440562750053538E-05</v>
+        <v>0.00012596645806486708</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -2153,7 +2153,7 @@
         <v>0.023895445565352016</v>
       </c>
       <c r="B60">
-        <v>-8.0179785806714328E-05</v>
+        <v>0.00012303403469945417</v>
       </c>
     </row>
     <row r="61" spans="1:2">
@@ -2161,7 +2161,7 @@
         <v>0.022809288948745104</v>
       </c>
       <c r="B61">
-        <v>-8.8808514649598715E-05</v>
+        <v>0.00011861776063917606</v>
       </c>
     </row>
     <row r="62" spans="1:2">
@@ -2169,7 +2169,7 @@
         <v>0.021723132332138195</v>
       </c>
       <c r="B62">
-        <v>-9.8379356636892315E-05</v>
+        <v>0.00011268259710216244</v>
       </c>
     </row>
     <row r="63" spans="1:2">
@@ -2177,7 +2177,7 @@
         <v>0.020636975715531285</v>
       </c>
       <c r="B63">
-        <v>-0.00010880634540764888</v>
+        <v>0.00010528587664408368</v>
       </c>
     </row>
     <row r="64" spans="1:2">
@@ -2185,7 +2185,7 @@
         <v>0.019550819098924376</v>
       </c>
       <c r="B64">
-        <v>-0.00011944921972439451</v>
+        <v>9.6854417170773083E-05</v>
       </c>
     </row>
     <row r="65" spans="1:2">
@@ -2193,7 +2193,7 @@
         <v>0.018464662482317467</v>
       </c>
       <c r="B65">
-        <v>-0.00012952914463052327</v>
+        <v>8.7907407925604737E-05</v>
       </c>
     </row>
     <row r="66" spans="1:2">
@@ -2201,7 +2201,7 @@
         <v>0.017378505865710558</v>
       </c>
       <c r="B66">
-        <v>-0.00013826728516942935</v>
+        <v>7.8964038151952638E-05</v>
       </c>
     </row>
     <row r="67" spans="1:2">
@@ -2209,7 +2209,7 @@
         <v>0.016292349249103645</v>
       </c>
       <c r="B67">
-        <v>-0.00014589092638686148</v>
+        <v>6.9872741474714321E-05</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -2217,7 +2217,7 @@
         <v>0.015206192632496738</v>
       </c>
       <c r="B68">
-        <v>-0.00015665183333798708</v>
+        <v>5.7798929044881232E-05</v>
       </c>
     </row>
     <row r="69" spans="1:2">
@@ -2225,7 +2225,7 @@
         <v>0.014120036015889827</v>
       </c>
       <c r="B69">
-        <v>-0.00017384304630063891</v>
+        <v>4.0547148958656577E-05</v>
       </c>
     </row>
     <row r="70" spans="1:2">
@@ -2233,7 +2233,7 @@
         <v>0.013033879399282919</v>
       </c>
       <c r="B70">
-        <v>-0.00019289822643389266</v>
+        <v>2.1161519566997156E-05</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -2241,7 +2241,7 @@
         <v>0.011947722782676008</v>
       </c>
       <c r="B71">
-        <v>-0.00020883878435317159</v>
+        <v>2.9609831681173594E-06</v>
       </c>
     </row>
     <row r="72" spans="1:2">
@@ -2249,7 +2249,7 @@
         <v>0.010861566166069097</v>
       </c>
       <c r="B72">
-        <v>-0.0002228965076180463</v>
+        <v>-1.4875792405490919E-05</v>
       </c>
     </row>
     <row r="73" spans="1:2">
@@ -2257,7 +2257,7 @@
         <v>0.0097754095494621881</v>
       </c>
       <c r="B73">
-        <v>-0.00023712949065399398</v>
+        <v>-3.3721021684124566E-05</v>
       </c>
     </row>
     <row r="74" spans="1:2">
@@ -2265,7 +2265,7 @@
         <v>0.0086892529328552789</v>
       </c>
       <c r="B74">
-        <v>-0.00025069067840597059</v>
+        <v>-5.3010174183512912E-05</v>
       </c>
     </row>
     <row r="75" spans="1:2">
@@ -2273,7 +2273,7 @@
         <v>0.0076030963162483688</v>
       </c>
       <c r="B75">
-        <v>-0.00026199082387196195</v>
+        <v>-7.1683935521531063E-05</v>
       </c>
     </row>
     <row r="76" spans="1:2">
@@ -2281,7 +2281,7 @@
         <v>0.00651693969964146</v>
       </c>
       <c r="B76">
-        <v>-0.00026937706174259482</v>
+        <v>-8.86406007392049E-05</v>
       </c>
     </row>
     <row r="77" spans="1:2">
@@ -2289,7 +2289,7 @@
         <v>0.0054307830830345486</v>
       </c>
       <c r="B77">
-        <v>-0.000271318931549613</v>
+        <v>-0.00010286007912762798</v>
       </c>
     </row>
     <row r="78" spans="1:2">
@@ -2297,7 +2297,7 @@
         <v>0.0043446264664276394</v>
       </c>
       <c r="B78">
-        <v>-0.00026683921049658809</v>
+        <v>-0.0001136911275550138</v>
       </c>
     </row>
     <row r="79" spans="1:2">
@@ -2305,7 +2305,7 @@
         <v>0.00325846984982073</v>
       </c>
       <c r="B79">
-        <v>-0.00025427306097049407</v>
+        <v>-0.00012002410315788001</v>
       </c>
     </row>
     <row r="80" spans="1:2">
@@ -2313,7 +2313,7 @@
         <v>0.0021723132332138197</v>
       </c>
       <c r="B80">
-        <v>-0.00023070078347659458</v>
+        <v>-0.00011991280858268982</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -2321,7 +2321,7 @@
         <v>0.0010861566166069099</v>
       </c>
       <c r="B81">
-        <v>-0.00018895459765106193</v>
+        <v>-0.0001085790080221506</v>
       </c>
     </row>
     <row r="82" spans="1:2">
